--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488196_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488196_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9129</v>
+        <v>3.6508</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0183</v>
+        <v>4.4854</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1054</v>
+        <v>-0.8346</v>
       </c>
       <c r="G2" t="n">
         <v>3.6297</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2907</v>
+        <v>-0.5528</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9103</v>
+        <v>0.3774</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.201</v>
+        <v>-0.9302</v>
       </c>
       <c r="V2" t="n">
         <v>0.9444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7248</v>
+        <v>0.878</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8177</v>
+        <v>1.8725</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0929</v>
+        <v>-0.9944</v>
       </c>
       <c r="G3" t="n">
         <v>0.5593</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5026</v>
+        <v>-0.3494</v>
       </c>
       <c r="T3" t="n">
-        <v>0.148</v>
+        <v>0.2027</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6506</v>
+        <v>-0.5521</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6289</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2189</v>
+        <v>-0.2195</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1427</v>
+        <v>-0.0447</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0762</v>
+        <v>-0.1747</v>
       </c>
       <c r="G4" t="n">
         <v>0.129</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3479</v>
+        <v>-0.3485</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1838</v>
+        <v>-0.2823</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9694</v>
+        <v>-0.6499</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5074</v>
+        <v>-0.4095</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.462</v>
+        <v>-0.2404</v>
       </c>
       <c r="G5" t="n">
         <v>1.8116</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0398</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4927</v>
+        <v>-0.2711</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6294</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6698</v>
+        <v>-1.695</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2452</v>
+        <v>-2.1473</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5754</v>
+        <v>0.4523</v>
       </c>
       <c r="G6" t="n">
         <v>0.2247</v>
@@ -922,13 +922,13 @@
         <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2089</v>
+        <v>-0.2341</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3071</v>
+        <v>-0.2092</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0982</v>
+        <v>-0.0249</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9444</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2179</v>
+        <v>-3.447</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2902</v>
+        <v>-2.6696</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9277</v>
+        <v>-0.7774</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4764</v>
+        <v>-0.6972</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5227</v>
+        <v>-0.5083</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9537</v>
+        <v>-0.1889</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3076</v>
+        <v>1.1359</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8206</v>
+        <v>0.4724</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.487</v>
+        <v>0.6635</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1688</v>
+        <v>-1.8331</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.9807</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4667</v>
+        <v>-0.8524</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6676</v>
+        <v>-2.9646</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1502</v>
+        <v>0.2148</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0174</v>
+        <v>-0.0998</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1677</v>
+        <v>0.3146</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.668</v>
+        <v>-3.5554</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7675</v>
+        <v>-1.5292</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9005</v>
+        <v>-2.0262</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6972</v>
+        <v>-3.4764</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5083</v>
+        <v>-1.5227</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1889</v>
+        <v>-1.9537</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1359</v>
+        <v>-1.3076</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4724</v>
+        <v>-0.8206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6635</v>
+        <v>-0.487</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8331</v>
+        <v>-2.1688</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9807</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8524</v>
+        <v>-1.4667</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.9646</v>
+        <v>1.6676</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0062</v>
+        <v>-0.4878</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1977</v>
+        <v>-0.2216</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1915</v>
+        <v>-0.2661</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.293</v>
+        <v>-4.4046</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9884</v>
+        <v>-1.9769</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3046</v>
+        <v>-2.4277</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7834</v>
@@ -1156,13 +1156,13 @@
         <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7685</v>
+        <v>-0.8801</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0174</v>
+        <v>0.0289</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7859</v>
+        <v>-0.909</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2589</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9287</v>
+        <v>-4.7755</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8435</v>
+        <v>-3.7888</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0852</v>
+        <v>-0.9867</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1415</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0461</v>
+        <v>-0.8929</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7113</v>
+        <v>-0.6566</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3348</v>
+        <v>-0.2363</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1693</v>
+        <v>-6.6681</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3091</v>
+        <v>-3.808</v>
       </c>
       <c r="F11" t="n">
         <v>-2.8601</v>
@@ -1312,10 +1312,10 @@
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.874</v>
+        <v>-1.3729</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0184</v>
+        <v>-0.5173</v>
       </c>
       <c r="U11" t="n">
         <v>-0.8556</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.215999999999999</v>
+        <v>-9.206200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1181</v>
+        <v>-7.8128</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0979</v>
+        <v>-1.3934</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4794</v>
@@ -1390,13 +1390,13 @@
         <v>2.4087</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2167</v>
+        <v>-1.2069</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1279</v>
+        <v>-0.8226</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0888</v>
+        <v>-0.3843</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2583</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.7133</v>
+        <v>-30.0924</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.3761</v>
+        <v>-17.8289</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.3371</v>
+        <v>-12.2633</v>
       </c>
       <c r="G13" t="n">
         <v>-8.389700000000001</v>
@@ -1468,13 +1468,13 @@
         <v>14.267</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.451599999999999</v>
+        <v>-6.830900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9805</v>
+        <v>-2.4335</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.4712</v>
+        <v>-4.3973</v>
       </c>
       <c r="V13" t="n">
         <v>-5.9783</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.56</v>
+        <v>8.340299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8698</v>
+        <v>4.1843</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6903</v>
+        <v>4.1561</v>
       </c>
       <c r="G14" t="n">
         <v>3.1627</v>
@@ -1546,13 +1546,13 @@
         <v>2.7793</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0263</v>
+        <v>1.8065</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6937</v>
+        <v>1.0082</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3325</v>
+        <v>0.7983</v>
       </c>
       <c r="V14" t="n">
         <v>1.8888</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4938</v>
+        <v>5.0261</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5261</v>
+        <v>2.3564</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9677</v>
+        <v>2.6696</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3146</v>
+        <v>2.579</v>
       </c>
       <c r="H15" t="n">
-        <v>1.373</v>
+        <v>-0.0522</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0583</v>
+        <v>2.6312</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7639</v>
+        <v>2.1087</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1679</v>
+        <v>0.1074</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.404</v>
+        <v>2.0013</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4493</v>
+        <v>0.4703</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.795</v>
+        <v>-0.1596</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3457</v>
+        <v>0.6299</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1499</v>
+        <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0679</v>
+        <v>0.5201</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2671</v>
+        <v>-0.0982</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2583</v>
+        <v>0.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2583</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1635</v>
+        <v>4.8238</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8461</v>
+        <v>1.7426</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3174</v>
+        <v>3.0811</v>
       </c>
       <c r="G16" t="n">
-        <v>2.579</v>
+        <v>1.3146</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0522</v>
+        <v>1.373</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6312</v>
+        <v>-0.0583</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1087</v>
+        <v>1.7639</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1074</v>
+        <v>2.1679</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0013</v>
+        <v>-0.404</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4703</v>
+        <v>-0.4493</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1596</v>
+        <v>-0.795</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6299</v>
+        <v>0.3457</v>
       </c>
       <c r="P16" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6676</v>
+        <v>3.1499</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6576</v>
+        <v>0.3979</v>
       </c>
       <c r="T16" t="n">
-        <v>1.108</v>
+        <v>0.0174</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4504</v>
+        <v>0.3805</v>
       </c>
       <c r="V16" t="n">
-        <v>0.63</v>
+        <v>1.2583</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2583</v>
       </c>
       <c r="X16" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7989</v>
+        <v>4.5623</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2992</v>
+        <v>2.9075</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4996</v>
+        <v>1.6548</v>
       </c>
       <c r="G17" t="n">
         <v>0.9347</v>
@@ -1780,13 +1780,13 @@
         <v>2.594</v>
       </c>
       <c r="S17" t="n">
-        <v>1.735</v>
+        <v>1.4985</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2349</v>
+        <v>0.8431</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5001</v>
+        <v>0.6553</v>
       </c>
       <c r="V17" t="n">
         <v>1.5733</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5111</v>
+        <v>4.5076</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4604</v>
+        <v>3.048</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0507</v>
+        <v>1.4596</v>
       </c>
       <c r="G18" t="n">
         <v>2.4265</v>
@@ -1858,13 +1858,13 @@
         <v>3.1499</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9709</v>
+        <v>0.0255</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9637</v>
+        <v>-0.3761</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0072</v>
+        <v>0.4016</v>
       </c>
       <c r="V18" t="n">
         <v>0.9439</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4345</v>
+        <v>2.8348</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7927</v>
+        <v>0.9885</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6419</v>
+        <v>1.8463</v>
       </c>
       <c r="G19" t="n">
         <v>0.9747</v>
@@ -1936,13 +1936,13 @@
         <v>2.594</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3549</v>
+        <v>0.0454</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6901</v>
+        <v>-0.4943</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3352</v>
+        <v>0.5397</v>
       </c>
       <c r="V19" t="n">
         <v>1.2589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7296</v>
+        <v>1.6608</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5128</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2424</v>
+        <v>2.3901</v>
       </c>
       <c r="G21" t="n">
         <v>0.9117</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>0.07729999999999999</v>
+        <v>1.0085</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1181</v>
+        <v>0.9016</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0408</v>
+        <v>0.1069</v>
       </c>
       <c r="V21" t="n">
         <v>-0.63</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6221</v>
+        <v>1.0546</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6221</v>
+        <v>0.5179</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.5366</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6221</v>
+        <v>-0.923</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-1.095</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6221</v>
+        <v>0.172</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6221</v>
+        <v>1.0026</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.4596</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6221</v>
+        <v>1.4622</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-1.9255</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.6354</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-1.2901</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.0511</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.6271</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4086</v>
+        <v>0.6221</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2241</v>
+        <v>0.6221</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1845</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.923</v>
+        <v>0.6221</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.095</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.172</v>
+        <v>0.6221</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0026</v>
+        <v>0.6221</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4596</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4622</v>
+        <v>0.6221</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9255</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6354</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2901</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4052</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07190000000000001</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2251</v>
+        <v>0.0446</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6661</v>
+        <v>-0.4702</v>
       </c>
       <c r="F24" t="n">
-        <v>0.441</v>
+        <v>0.5148</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2197</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0055</v>
+        <v>0.2643</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0547</v>
+        <v>0.1411</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.886</v>
+        <v>-1.6941</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0829</v>
+        <v>-0.8663</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8031</v>
+        <v>-0.8277</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9743</v>
@@ -2404,13 +2404,13 @@
         <v>1.4823</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3652</v>
+        <v>0.5571</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8344</v>
+        <v>0.051</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5061</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5738</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1625</v>
+        <v>-2.0286</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.2466</v>
+        <v>-4.1693</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0841</v>
+        <v>2.1408</v>
       </c>
       <c r="G26" t="n">
         <v>-3.6787</v>
@@ -2482,13 +2482,13 @@
         <v>2.0382</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0726</v>
+        <v>1.2065</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1554</v>
+        <v>0.9218</v>
       </c>
       <c r="U26" t="n">
-        <v>0.228</v>
+        <v>0.2848</v>
       </c>
       <c r="V26" t="n">
         <v>0.6289</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>30.3368</v>
+        <v>31.64260000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>12.0204</v>
+        <v>12.0205</v>
       </c>
       <c r="F27" t="n">
-        <v>18.3165</v>
+        <v>19.6221</v>
       </c>
       <c r="G27" t="n">
         <v>8.018599999999999</v>
@@ -2536,7 +2536,7 @@
         <v>15.3662</v>
       </c>
       <c r="K27" t="n">
-        <v>4.961199999999999</v>
+        <v>4.961200000000001</v>
       </c>
       <c r="L27" t="n">
         <v>10.4049</v>
@@ -2560,13 +2560,13 @@
         <v>23.161</v>
       </c>
       <c r="S27" t="n">
-        <v>7.075799999999999</v>
+        <v>8.381399999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>4.2594</v>
+        <v>4.259300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>2.8163</v>
+        <v>4.1221</v>
       </c>
       <c r="V27" t="n">
         <v>5.9783</v>
